--- a/artfynd/A 7434-2025 artfynd.xlsx
+++ b/artfynd/A 7434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109581499</v>
+        <v>109584904</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alanen Salmijärvi, Nb</t>
+          <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>872586.4055945589</v>
+        <v>872263</v>
       </c>
       <c r="R2" t="n">
-        <v>7402014.310981632</v>
+        <v>7401729</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,66 +775,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109584843</v>
+        <v>110352224</v>
       </c>
       <c r="B3" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>872339.8959747562</v>
+        <v>872529</v>
       </c>
       <c r="R3" t="n">
-        <v>7401899.048881114</v>
+        <v>7401958</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109580891</v>
+        <v>109581056</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,13 +920,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>872644.3198499915</v>
+        <v>872679</v>
       </c>
       <c r="R4" t="n">
-        <v>7402016.101456527</v>
+        <v>7402008</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +955,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +965,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +980,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109584970</v>
+        <v>110352310</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +1003,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>872365.6865177316</v>
+        <v>871718</v>
       </c>
       <c r="R5" t="n">
-        <v>7401896.486874578</v>
+        <v>7401842</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,49 +1077,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109581334</v>
+        <v>109580959</v>
       </c>
       <c r="B6" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>872659.2410485148</v>
+        <v>872679</v>
       </c>
       <c r="R6" t="n">
-        <v>7402013.280857304</v>
+        <v>7402008</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1203,7 +1160,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1170,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,51 +1197,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109584765</v>
+        <v>109581499</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Likakurunvuoma, Nb</t>
+          <t>Alanen Salmijärvi, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>872342.1795711179</v>
+        <v>872586</v>
       </c>
       <c r="R7" t="n">
-        <v>7401879.185849068</v>
+        <v>7402015</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1268,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1278,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,37 +1305,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109583481</v>
+        <v>109589676</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>872438.7101048212</v>
+        <v>872263</v>
       </c>
       <c r="R8" t="n">
-        <v>7401822.451522982</v>
+        <v>7401729</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1429,7 +1376,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1386,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,49 +1413,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109587663</v>
+        <v>109591436</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1516,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>872056.2819645405</v>
+        <v>872865</v>
       </c>
       <c r="R9" t="n">
-        <v>7401693.665084289</v>
+        <v>7401740</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1561,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,63 +1521,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109580927</v>
+        <v>110352289</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Alanen Salmijärvi, Nb</t>
+          <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>872647.1055189725</v>
+        <v>872429</v>
       </c>
       <c r="R10" t="n">
-        <v>7402025.354246896</v>
+        <v>7401685</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,66 +1606,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109585029</v>
+        <v>110352290</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>872313.0231759783</v>
+        <v>872102</v>
       </c>
       <c r="R11" t="n">
-        <v>7401870.803298575</v>
+        <v>7401860</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,22 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,31 +1703,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109589676</v>
+        <v>110352291</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1857,20 +1744,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>872262.8657010754</v>
+        <v>872046</v>
       </c>
       <c r="R12" t="n">
-        <v>7401728.055444526</v>
+        <v>7401782</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,22 +1780,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,66 +1800,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109589896</v>
+        <v>110352292</v>
       </c>
       <c r="B13" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>872652.7044640286</v>
+        <v>871856</v>
       </c>
       <c r="R13" t="n">
-        <v>7401751.360719047</v>
+        <v>7401550</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,22 +1877,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,27 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109584904</v>
+        <v>110352293</v>
       </c>
       <c r="B14" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,42 +1920,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>872262.8657010754</v>
+        <v>871853</v>
       </c>
       <c r="R14" t="n">
-        <v>7401728.055444526</v>
+        <v>7401572</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,22 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,27 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110352283</v>
+        <v>110352294</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,46 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>872686.1980702648</v>
+        <v>871789</v>
       </c>
       <c r="R15" t="n">
-        <v>7401718.77633446</v>
+        <v>7401785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,28 +2074,17 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2291,37 +2103,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110352267</v>
+        <v>110352295</v>
       </c>
       <c r="B16" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>872016.0037818676</v>
+        <v>871734</v>
       </c>
       <c r="R16" t="n">
-        <v>7401866.138258775</v>
+        <v>7401811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,19 +2171,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,19 +2200,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110352297</v>
+        <v>110352296</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2443,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>872071.0404314095</v>
+        <v>872016</v>
       </c>
       <c r="R17" t="n">
-        <v>7401787.646684287</v>
+        <v>7401866</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2268,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,37 +2297,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110352269</v>
+        <v>110352297</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2555,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>872428.2641931013</v>
+        <v>872071</v>
       </c>
       <c r="R18" t="n">
-        <v>7401923.513196967</v>
+        <v>7401788</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,19 +2365,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,37 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110352252</v>
+        <v>110352298</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2667,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>872158.959245434</v>
+        <v>872365</v>
       </c>
       <c r="R19" t="n">
-        <v>7401737.80667756</v>
+        <v>7401841</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,19 +2462,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,37 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110352270</v>
+        <v>110352299</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2779,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>872579.2766184323</v>
+        <v>872596</v>
       </c>
       <c r="R20" t="n">
-        <v>7402022.221261375</v>
+        <v>7402042</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,19 +2559,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,37 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110352273</v>
+        <v>110352300</v>
       </c>
       <c r="B21" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2891,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>872002.9214147618</v>
+        <v>872639</v>
       </c>
       <c r="R21" t="n">
-        <v>7401717.921293773</v>
+        <v>7402041</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,19 +2656,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,53 +2685,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110352268</v>
+        <v>109581334</v>
       </c>
       <c r="B22" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Likakurunvuoma, Nb</t>
+          <t>Alanen Salmijärvi, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>872253.1779717042</v>
+        <v>872659</v>
       </c>
       <c r="R22" t="n">
-        <v>7401928.064118479</v>
+        <v>7402014</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3033,22 +2751,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,65 +2781,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110352294</v>
+        <v>109584843</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>871789.0876757605</v>
+        <v>872339</v>
       </c>
       <c r="R23" t="n">
-        <v>7401785.044630839</v>
+        <v>7401899</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3145,22 +2859,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3175,27 +2889,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110352251</v>
+        <v>109583481</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3203,37 +2912,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>872079.2612414506</v>
+        <v>872438</v>
       </c>
       <c r="R24" t="n">
-        <v>7401774.637579379</v>
+        <v>7401823</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3257,22 +2967,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,65 +2997,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110352293</v>
+        <v>109585029</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>871853.036014237</v>
+        <v>872313</v>
       </c>
       <c r="R25" t="n">
-        <v>7401571.787869599</v>
+        <v>7401870</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3369,22 +3075,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,27 +3105,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110352275</v>
+        <v>110352239</v>
       </c>
       <c r="B26" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,21 +3128,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>871867.711896678</v>
+        <v>872030</v>
       </c>
       <c r="R26" t="n">
-        <v>7401508.005278299</v>
+        <v>7401765</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3484,19 +3185,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,37 +3214,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110352237</v>
+        <v>110352308</v>
       </c>
       <c r="B27" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>872036.8534421038</v>
+        <v>872032</v>
       </c>
       <c r="R27" t="n">
-        <v>7401876.218543597</v>
+        <v>7401777</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,19 +3282,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,15 +3311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110352253</v>
+        <v>109584972</v>
       </c>
       <c r="B28" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,37 +3322,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>872183.3300152288</v>
+        <v>872359</v>
       </c>
       <c r="R28" t="n">
-        <v>7401853.26038431</v>
+        <v>7401904</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3705,22 +3382,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3735,31 +3412,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Jon Mihkkal Inga</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Jon Mihkkal Inga</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110352259</v>
+        <v>110352257</v>
       </c>
       <c r="B29" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3787,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>872139.4517165683</v>
+        <v>872743</v>
       </c>
       <c r="R29" t="n">
-        <v>7401777.531099883</v>
+        <v>7401759</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3820,19 +3492,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,15 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110352248</v>
+        <v>110352258</v>
       </c>
       <c r="B30" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,21 +3532,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3556,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>871759.5004132842</v>
+        <v>872413</v>
       </c>
       <c r="R30" t="n">
-        <v>7401830.669261035</v>
+        <v>7401691</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,19 +3589,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,37 +3618,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110352290</v>
+        <v>110352259</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>872102.0461973262</v>
+        <v>872140</v>
       </c>
       <c r="R31" t="n">
-        <v>7401860.019874323</v>
+        <v>7401777</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4044,19 +3686,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,15 +3715,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110352254</v>
+        <v>110352260</v>
       </c>
       <c r="B32" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4099,21 +3726,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +3750,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>872204.6734910461</v>
+        <v>872093</v>
       </c>
       <c r="R32" t="n">
-        <v>7401898.507746806</v>
+        <v>7401844</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,19 +3783,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4195,15 +3812,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110352256</v>
+        <v>110352261</v>
       </c>
       <c r="B33" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4211,21 +3823,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4235,10 +3847,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>872460.9337284705</v>
+        <v>872030</v>
       </c>
       <c r="R33" t="n">
-        <v>7401962.630287396</v>
+        <v>7401765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,19 +3880,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4307,37 +3909,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110352296</v>
+        <v>110352262</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4347,10 +3944,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>872016.0037818676</v>
+        <v>871861</v>
       </c>
       <c r="R34" t="n">
-        <v>7401866.138258775</v>
+        <v>7401510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4380,19 +3977,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4422,16 +4009,11 @@
         <v>110352265</v>
       </c>
       <c r="B35" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4459,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>871853.3204447492</v>
+        <v>871853</v>
       </c>
       <c r="R35" t="n">
-        <v>7401542.776755353</v>
+        <v>7401543</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4492,19 +4074,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4531,15 +4103,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110352241</v>
+        <v>110352266</v>
       </c>
       <c r="B36" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4547,21 +4114,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4571,10 +4138,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>871887.4526498909</v>
+        <v>871806</v>
       </c>
       <c r="R36" t="n">
-        <v>7401535.284248191</v>
+        <v>7401816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4604,19 +4171,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,37 +4200,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>110352299</v>
+        <v>110352267</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4683,10 +4235,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>872596.8533211274</v>
+        <v>872016</v>
       </c>
       <c r="R37" t="n">
-        <v>7402041.545192691</v>
+        <v>7401866</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4716,19 +4268,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4755,15 +4297,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>110352249</v>
+        <v>110352268</v>
       </c>
       <c r="B38" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,21 +4308,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4795,10 +4332,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>871878.3030424744</v>
+        <v>872254</v>
       </c>
       <c r="R38" t="n">
-        <v>7401845.106712915</v>
+        <v>7401928</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4828,19 +4365,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4867,15 +4394,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>110352305</v>
+        <v>110352269</v>
       </c>
       <c r="B39" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,21 +4405,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4907,10 +4429,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>872451.9080311639</v>
+        <v>872428</v>
       </c>
       <c r="R39" t="n">
-        <v>7401966.653339936</v>
+        <v>7401923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4940,19 +4462,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4979,19 +4491,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>110352262</v>
+        <v>110352270</v>
       </c>
       <c r="B40" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5019,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>871860.5938579786</v>
+        <v>872579</v>
       </c>
       <c r="R40" t="n">
-        <v>7401509.867907663</v>
+        <v>7402022</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,19 +4559,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5091,15 +4588,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>110352245</v>
+        <v>109583008</v>
       </c>
       <c r="B41" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,37 +4599,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>871793.2460697003</v>
+        <v>872472</v>
       </c>
       <c r="R41" t="n">
-        <v>7401781.168659667</v>
+        <v>7401850</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5161,22 +4654,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,27 +4684,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>110352244</v>
+        <v>109589844</v>
       </c>
       <c r="B42" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,37 +4707,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>871856.9393482964</v>
+        <v>872596</v>
       </c>
       <c r="R42" t="n">
-        <v>7401578.77064613</v>
+        <v>7401742</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5273,22 +4772,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5303,77 +4802,61 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>110352284</v>
+        <v>109591444</v>
       </c>
       <c r="B43" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>872078.285623329</v>
+        <v>872864</v>
       </c>
       <c r="R43" t="n">
-        <v>7401772.891897229</v>
+        <v>7401741</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5397,22 +4880,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5421,34 +4904,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>110352308</v>
+        <v>110352226</v>
       </c>
       <c r="B44" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5456,21 +4933,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5480,10 +4957,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>872032.4707695446</v>
+        <v>872208</v>
       </c>
       <c r="R44" t="n">
-        <v>7401777.18773846</v>
+        <v>7401775</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5513,19 +4990,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5552,50 +5019,61 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>110352257</v>
+        <v>110352228</v>
       </c>
       <c r="B45" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>872742.4832542776</v>
+        <v>871891</v>
       </c>
       <c r="R45" t="n">
-        <v>7401759.483955508</v>
+        <v>7401572</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5625,19 +5103,14 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Uppflygande.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5664,15 +5137,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>110352272</v>
+        <v>110352229</v>
       </c>
       <c r="B46" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5680,21 +5148,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5704,10 +5172,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>872757.6859652263</v>
+        <v>871856</v>
       </c>
       <c r="R46" t="n">
-        <v>7401748.631772862</v>
+        <v>7401535</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,19 +5205,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5776,37 +5234,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>110352224</v>
+        <v>110352231</v>
       </c>
       <c r="B47" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5816,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>872530.1257209047</v>
+        <v>871853</v>
       </c>
       <c r="R47" t="n">
-        <v>7401958.682721399</v>
+        <v>7401569</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,19 +5302,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5888,37 +5331,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>110352292</v>
+        <v>110352232</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5928,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>871856.3769793685</v>
+        <v>872381</v>
       </c>
       <c r="R48" t="n">
-        <v>7401550.048651446</v>
+        <v>7401861</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5961,19 +5399,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,37 +5428,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>110352258</v>
+        <v>110352233</v>
       </c>
       <c r="B49" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6040,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>872413.2668344975</v>
+        <v>872446</v>
       </c>
       <c r="R49" t="n">
-        <v>7401691.110938008</v>
+        <v>7401948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6073,19 +5496,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6112,15 +5525,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>110352302</v>
+        <v>110352234</v>
       </c>
       <c r="B50" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6128,21 +5536,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6152,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>871853.0263343945</v>
+        <v>872444</v>
       </c>
       <c r="R50" t="n">
-        <v>7401577.838512736</v>
+        <v>7401953</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6185,19 +5593,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6224,37 +5622,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>110352295</v>
+        <v>110352235</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6264,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>871735.0676543417</v>
+        <v>872550</v>
       </c>
       <c r="R51" t="n">
-        <v>7401811.231889402</v>
+        <v>7401980</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6297,19 +5690,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6336,15 +5719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110352306</v>
+        <v>110352236</v>
       </c>
       <c r="B52" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6352,34 +5730,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>872460.9337284705</v>
+        <v>872608</v>
       </c>
       <c r="R52" t="n">
-        <v>7401962.630287396</v>
+        <v>7402046</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6409,19 +5807,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6448,15 +5836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110352247</v>
+        <v>109581257</v>
       </c>
       <c r="B53" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6464,37 +5847,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>102613</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Likakurunvuoma, Nb</t>
+          <t>Alanen Salmijärvi, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>871724.6925151362</v>
+        <v>872646</v>
       </c>
       <c r="R53" t="n">
-        <v>7401816.285272104</v>
+        <v>7402025</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6518,22 +5902,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6548,27 +5932,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>110352303</v>
+        <v>110352277</v>
       </c>
       <c r="B54" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6576,21 +5955,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6600,10 +5979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>872447.0637659379</v>
+        <v>872400</v>
       </c>
       <c r="R54" t="n">
-        <v>7401954.701530484</v>
+        <v>7401900</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6633,19 +6012,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6672,15 +6041,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>110352274</v>
+        <v>110352278</v>
       </c>
       <c r="B55" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6688,21 +6052,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6712,10 +6076,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>871970.8201866623</v>
+        <v>872561</v>
       </c>
       <c r="R55" t="n">
-        <v>7401665.571619499</v>
+        <v>7401990</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,19 +6109,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6784,15 +6138,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>110352289</v>
+        <v>110352237</v>
       </c>
       <c r="B56" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6800,21 +6149,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6824,10 +6173,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>872429.4114879651</v>
+        <v>872036</v>
       </c>
       <c r="R56" t="n">
-        <v>7401685.226157704</v>
+        <v>7401876</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6857,19 +6206,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6896,37 +6235,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>110352291</v>
+        <v>110352302</v>
       </c>
       <c r="B57" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6936,10 +6270,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>872046.3208336993</v>
+        <v>871853</v>
       </c>
       <c r="R57" t="n">
-        <v>7401782.287589862</v>
+        <v>7401578</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6969,19 +6303,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7008,15 +6332,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>110352239</v>
+        <v>110352303</v>
       </c>
       <c r="B58" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7024,21 +6343,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7048,10 +6367,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>872030.4543363631</v>
+        <v>872447</v>
       </c>
       <c r="R58" t="n">
-        <v>7401765.215295625</v>
+        <v>7401955</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7081,19 +6400,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7120,15 +6429,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>110352243</v>
+        <v>110352305</v>
       </c>
       <c r="B59" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7136,21 +6440,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7160,10 +6464,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>871855.0483325503</v>
+        <v>872452</v>
       </c>
       <c r="R59" t="n">
-        <v>7401553.903812508</v>
+        <v>7401966</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7193,19 +6497,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7232,37 +6526,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>110352300</v>
+        <v>110352306</v>
       </c>
       <c r="B60" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7272,10 +6561,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>872638.9034159677</v>
+        <v>872460</v>
       </c>
       <c r="R60" t="n">
-        <v>7402041.187707946</v>
+        <v>7401963</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7305,19 +6594,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7344,50 +6623,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>110352260</v>
+        <v>110352283</v>
       </c>
       <c r="B61" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>872093.3196143582</v>
+        <v>872685</v>
       </c>
       <c r="R61" t="n">
-        <v>7401843.912864308</v>
+        <v>7401719</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7417,27 +6703,18 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7456,50 +6733,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>110352240</v>
+        <v>110352284</v>
       </c>
       <c r="B62" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Likakurunvuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>872693.7185518006</v>
+        <v>872078</v>
       </c>
       <c r="R62" t="n">
-        <v>7401755.704120613</v>
+        <v>7401773</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7529,27 +6813,18 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7568,15 +6843,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>110352255</v>
+        <v>110352272</v>
       </c>
       <c r="B63" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7584,21 +6854,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7608,10 +6878,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>872223.475517925</v>
+        <v>872758</v>
       </c>
       <c r="R63" t="n">
-        <v>7401929.694435073</v>
+        <v>7401749</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7641,19 +6911,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7680,37 +6940,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>110352266</v>
+        <v>110352273</v>
       </c>
       <c r="B64" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7720,10 +6975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>871805.858204409</v>
+        <v>872003</v>
       </c>
       <c r="R64" t="n">
-        <v>7401816.357206343</v>
+        <v>7401718</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7753,19 +7008,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7792,15 +7037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>110352246</v>
+        <v>110352274</v>
       </c>
       <c r="B65" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7808,21 +7048,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7832,10 +7072,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>871787.318648403</v>
+        <v>871970</v>
       </c>
       <c r="R65" t="n">
-        <v>7401783.191921631</v>
+        <v>7401665</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7865,19 +7105,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7904,37 +7134,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>110352298</v>
+        <v>110352275</v>
       </c>
       <c r="B66" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7944,10 +7169,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>872365.4414770559</v>
+        <v>871867</v>
       </c>
       <c r="R66" t="n">
-        <v>7401841.585346792</v>
+        <v>7401508</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7977,19 +7202,9 @@
           <t>2023-06-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2023-06-12</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8016,53 +7231,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>110352261</v>
+        <v>109580891</v>
       </c>
       <c r="B67" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Likakurunvuoma, Nb</t>
+          <t>Alanen Salmijärvi, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>872030.4543363631</v>
+        <v>872644</v>
       </c>
       <c r="R67" t="n">
-        <v>7401765.215295625</v>
+        <v>7402016</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8086,22 +7297,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8116,68 +7327,67 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>109584972</v>
+        <v>109580927</v>
       </c>
       <c r="B68" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Likakurunvuoma, Nb</t>
+          <t>Alanen Salmijärvi, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>872359</v>
+        <v>872647</v>
       </c>
       <c r="R68" t="n">
-        <v>7401904</v>
+        <v>7402025</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8209,7 +7419,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8219,7 +7429,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8234,15 +7444,1911 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jon Mihkkal Inga</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jon Mihkkal Inga</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>109584765</v>
+      </c>
+      <c r="B69" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>872342</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7401880</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>109584970</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>872366</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7401896</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>109587663</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>872056</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7401694</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>109589896</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>872653</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7401751</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>110352240</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>872693</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7401756</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>110352241</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>871888</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7401535</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>110352243</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>871855</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7401554</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>110352244</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>871856</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7401579</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>110352245</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>871793</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7401781</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>110352246</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>871787</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7401783</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>110352247</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>871724</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7401816</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>110352248</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>871759</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7401831</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>110352249</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>871878</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7401845</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>110352251</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>872080</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7401775</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>110352252</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>872159</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7401738</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>110352253</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>872183</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7401853</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>110352254</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>872205</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7401899</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>110352255</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>872223</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7401930</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>110352256</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Likakurunvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>872460</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7401963</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-06-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7434-2025 artfynd.xlsx
+++ b/artfynd/A 7434-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584904</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109581056</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352310</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109580959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109581499</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589676</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109591436</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352289</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352290</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352291</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352292</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2003,6 +2068,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352293</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352295</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352296</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2488,6 +2578,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352298</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2585,6 +2680,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352299</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352300</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2790,6 +2895,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109581334</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3006,6 +3121,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109583481</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3114,6 +3234,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585029</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3211,6 +3336,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352239</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3308,6 +3438,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352308</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584972</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352257</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3615,6 +3760,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352258</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352259</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3809,6 +3964,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352260</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352261</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4003,6 +4168,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352262</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4100,6 +4270,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352265</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4197,6 +4372,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352266</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4294,6 +4474,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352267</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4391,6 +4576,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352268</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4488,6 +4678,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352269</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4585,6 +4780,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352270</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4693,6 +4893,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109583008</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4811,6 +5016,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589844</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4919,6 +5129,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109591444</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5016,6 +5231,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352226</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5134,6 +5354,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352228</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5231,6 +5456,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352229</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5328,6 +5558,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352231</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5425,6 +5660,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352232</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5522,6 +5762,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352233</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5619,6 +5864,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352234</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5716,6 +5966,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352235</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5833,6 +6088,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352236</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5941,6 +6201,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109581257</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6038,6 +6303,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352277</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6135,6 +6405,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352278</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6232,6 +6507,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352237</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6329,6 +6609,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352302</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6426,6 +6711,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352303</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6523,6 +6813,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352305</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6620,6 +6915,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352306</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6730,6 +7030,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352283</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6840,6 +7145,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352284</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6937,6 +7247,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352272</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7034,6 +7349,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352273</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7131,6 +7451,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352274</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7228,6 +7553,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352275</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7336,6 +7666,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109580891</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7453,6 +7788,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109580927</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7561,6 +7901,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584765</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7669,6 +8014,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584970</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7786,6 +8136,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109587663</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7894,6 +8249,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109589896</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7991,6 +8351,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352240</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8088,6 +8453,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352241</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8185,6 +8555,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352243</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8282,6 +8657,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352244</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8379,6 +8759,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352245</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8476,6 +8861,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352246</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8573,6 +8963,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352247</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8670,6 +9065,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352248</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8767,6 +9167,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352249</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8864,6 +9269,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352251</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8961,6 +9371,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352252</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9058,6 +9473,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352253</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9155,6 +9575,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352254</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9252,6 +9677,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352255</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9349,8 +9779,101 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110352256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>